--- a/Result/profitability/6222.xlsx
+++ b/Result/profitability/6222.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08500000000000002</v>
+        <v>-0.06125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.335000000000001</v>
+        <v>21.35125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05625000000000001</v>
+        <v>-0.04875000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>19.6425</v>
+        <v>17.0725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0525</v>
+        <v>-0.04125000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>15.165</v>
+        <v>16.9575</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-6.74</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.87875</v>
+        <v>-0.875</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7525</v>
+        <v>1.317500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.85</v>
+        <v>-0.8412499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7899999999999987</v>
+        <v>2.673750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
         <v>-0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.925</v>
+        <v>-0.91625</v>
       </c>
       <c r="N7" t="n">
-        <v>2.201249999999999</v>
+        <v>2.93125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>-1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.08875</v>
+        <v>-1.08625</v>
       </c>
       <c r="N8" t="n">
-        <v>2.136249999999999</v>
+        <v>2.27</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>-1.1175</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9312499999999986</v>
+        <v>0.9312500000000004</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>-1.09625</v>
       </c>
       <c r="N10" t="n">
-        <v>1.804999999999999</v>
+        <v>1.805</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         <v>-1.06375</v>
       </c>
       <c r="N11" t="n">
-        <v>2.497499999999999</v>
+        <v>2.4975</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>-1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>4.064999999999999</v>
+        <v>4.065</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1048.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.10625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-2.691250000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04560954816709284</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.03000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1242413423777222</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
